--- a/data/trans_orig/IP36-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP36-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>593</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31619</t>
+          <t>31834</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46872</t>
+          <t>46541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33657</t>
+          <t>32808</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48125</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69256</t>
+          <t>69682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90903</t>
+          <t>90642</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,01%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12009</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24917</t>
+          <t>25351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40013</t>
+          <t>39494</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41751</t>
+          <t>41461</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>56265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76672</t>
+          <t>77224</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143378</t>
+          <t>144144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175337</t>
+          <t>175478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163345</t>
+          <t>163017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196562</t>
+          <t>196910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>314892</t>
+          <t>314253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>363757</t>
+          <t>363225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17838</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>486</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35231</t>
+          <t>35028</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>22378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40438</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45943</t>
+          <t>45842</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68985</t>
+          <t>69592</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -2545,12 +2545,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204401</t>
+          <t>203578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235705</t>
+          <t>235813</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2560,49 +2560,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>56,75%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>253695</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>237240</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>270595</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>53,19%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>49,74%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>56,73%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>253695</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>236997</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>271699</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>53,19%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>49,69%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>56,96%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>716</t>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>449103</t>
+          <t>449503</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>498869</t>
+          <t>498496</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,85%</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28697</t>
+          <t>29037</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>46263</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21882</t>
+          <t>22167</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38082</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55446</t>
+          <t>55825</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79667</t>
+          <t>79570</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>13707</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21989</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117538</t>
+          <t>117200</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>135570</t>
+          <t>135522</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>107404</t>
+          <t>107243</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>125299</t>
+          <t>125110</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>230077</t>
+          <t>230782</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>256927</t>
+          <t>256623</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -3796,12 +3796,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16612</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>558</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>216599</t>
+          <t>215868</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>257210</t>
+          <t>256280</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>230203</t>
+          <t>229910</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>270110</t>
+          <t>271099</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>459491</t>
+          <t>459850</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>513421</t>
+          <t>516895</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>19279</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>17338</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>16307</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31892</t>
+          <t>32292</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>34105</t>
+          <t>32945</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>54606</t>
+          <t>54263</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>35118</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>55475</t>
+          <t>56302</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>74878</t>
+          <t>75614</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>104934</t>
+          <t>104166</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>356690</t>
+          <t>357347</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>398723</t>
+          <t>401168</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>385610</t>
+          <t>383873</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>427566</t>
+          <t>427522</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>755079</t>
+          <t>751705</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>811445</t>
+          <t>812228</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>606</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5387,12 +5387,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31082</t>
+          <t>30747</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46103</t>
+          <t>45510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>45247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64740</t>
+          <t>65676</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86254</t>
+          <t>87417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5520,77 +5520,77 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5493</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3090</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>7423</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>4,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5304</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1135</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6754</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>31660</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>15730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>28975</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36525</t>
+          <t>36707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55857</t>
+          <t>56298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19612</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34117</t>
+          <t>34127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29212</t>
+          <t>28755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38816</t>
+          <t>38380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58106</t>
+          <t>58393</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13058</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6310,47 +6310,47 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3735</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1431</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>7778</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>3735</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>8092</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92579</t>
+          <t>91971</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122608</t>
+          <t>123677</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107943</t>
+          <t>107755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139692</t>
+          <t>139237</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>209826</t>
+          <t>207633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252187</t>
+          <t>250836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13460</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>125774</t>
+          <t>125215</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>157950</t>
+          <t>158329</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135949</t>
+          <t>136538</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>169908</t>
+          <t>171309</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>271196</t>
+          <t>271624</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>318811</t>
+          <t>317265</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>173844</t>
+          <t>173796</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209452</t>
+          <t>209433</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>187224</t>
+          <t>187522</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>223815</t>
+          <t>225172</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>371957</t>
+          <t>373262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>421922</t>
+          <t>422778</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>19139</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>34391</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>17327</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33503</t>
+          <t>32533</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41390</t>
+          <t>41188</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>63859</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7768,12 +7768,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25661</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>43160</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26411</t>
+          <t>26699</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44249</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>56406</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>80655</t>
+          <t>81927</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -7881,12 +7881,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>93331</t>
+          <t>93617</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>114320</t>
+          <t>113455</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>97281</t>
+          <t>98538</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>119185</t>
+          <t>119488</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7931,12 +7931,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>197265</t>
+          <t>195797</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>227027</t>
+          <t>227625</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>461</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -8224,12 +8224,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -8337,12 +8337,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8372,12 +8372,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18136</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -8450,12 +8450,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>153852</t>
+          <t>154408</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>193129</t>
+          <t>192674</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>165841</t>
+          <t>164581</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>206126</t>
+          <t>205495</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8500,12 +8500,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>331461</t>
+          <t>331127</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>382980</t>
+          <t>382963</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -8563,12 +8563,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>179035</t>
+          <t>180616</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>219597</t>
+          <t>220510</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>188562</t>
+          <t>187457</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>229246</t>
+          <t>229066</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>383167</t>
+          <t>381758</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>438179</t>
+          <t>437241</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -8902,12 +8902,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>300626</t>
+          <t>299462</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>343846</t>
+          <t>341932</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>313702</t>
+          <t>314632</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>358127</t>
+          <t>359655</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>627526</t>
+          <t>628719</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>689353</t>
+          <t>690204</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -9702,12 +9702,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>18744</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22115</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9772,12 +9772,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>21645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37653</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -10041,12 +10041,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22294</t>
+          <t>22149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34373</t>
+          <t>34821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10056,12 +10056,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10076,12 +10076,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>34838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10091,12 +10091,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46560</t>
+          <t>46060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65746</t>
+          <t>64649</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18095</t>
+          <t>18617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10169,12 +10169,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26046</t>
+          <t>26570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24212</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40769</t>
+          <t>41416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -10497,12 +10497,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10532,12 +10532,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>15267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -10610,12 +10610,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -10645,12 +10645,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18937</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>27360</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -10723,12 +10723,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72552</t>
+          <t>71848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99211</t>
+          <t>98341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10738,12 +10738,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10758,12 +10758,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80496</t>
+          <t>79283</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109577</t>
+          <t>107674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>157755</t>
+          <t>159374</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>197597</t>
+          <t>196375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -10836,12 +10836,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>19553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27947</t>
+          <t>27583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10921,12 +10921,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -10949,12 +10949,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>736</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -11062,12 +11062,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>137763</t>
+          <t>137549</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>169945</t>
+          <t>168682</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120110</t>
+          <t>119686</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>152870</t>
+          <t>152778</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>266824</t>
+          <t>266296</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>313409</t>
+          <t>310943</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11147,12 +11147,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -11175,12 +11175,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196818</t>
+          <t>195539</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229304</t>
+          <t>230470</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11210,12 +11210,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209780</t>
+          <t>211675</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246385</t>
+          <t>247885</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11245,12 +11245,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>415423</t>
+          <t>416481</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466605</t>
+          <t>465261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -11744,12 +11744,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12767</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>27098</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11779,12 +11779,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15428</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>29910</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11794,12 +11794,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11814,12 +11814,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31651</t>
+          <t>31961</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51118</t>
+          <t>51368</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11829,12 +11829,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11892,12 +11892,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11927,12 +11927,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8347</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -12083,12 +12083,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29055</t>
+          <t>29851</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47870</t>
+          <t>47489</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12118,12 +12118,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>25271</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40309</t>
+          <t>41604</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>58397</t>
+          <t>57468</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>84205</t>
+          <t>81967</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12168,12 +12168,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -12196,12 +12196,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>102261</t>
+          <t>104471</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>123993</t>
+          <t>125059</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12211,12 +12211,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>116605</t>
+          <t>116909</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>138315</t>
+          <t>138267</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12246,12 +12246,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>227755</t>
+          <t>227352</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>256519</t>
+          <t>257048</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12281,12 +12281,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,36%</t>
         </is>
       </c>
     </row>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -12539,12 +12539,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13633</t>
+          <t>14076</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12554,12 +12554,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12574,12 +12574,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12609,12 +12609,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>13216</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12667,12 +12667,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12687,12 +12687,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>22284</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12702,12 +12702,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12722,12 +12722,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>31785</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -12765,12 +12765,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>99869</t>
+          <t>99790</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>132611</t>
+          <t>132157</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>114685</t>
+          <t>115329</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>148753</t>
+          <t>150057</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12835,12 +12835,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>224819</t>
+          <t>226281</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>273265</t>
+          <t>274890</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -12878,12 +12878,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>17861</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12913,12 +12913,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>28441</t>
+          <t>28088</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12928,12 +12928,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22843</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>41170</t>
+          <t>40634</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>749</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13026,12 +13026,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13041,12 +13041,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -13104,12 +13104,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>199172</t>
+          <t>199816</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>238265</t>
+          <t>239590</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13119,12 +13119,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13139,12 +13139,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>178115</t>
+          <t>174875</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>219356</t>
+          <t>215790</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>387580</t>
+          <t>386818</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>444546</t>
+          <t>443862</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -13217,12 +13217,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>318502</t>
+          <t>320693</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>362771</t>
+          <t>363036</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13252,12 +13252,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>354717</t>
+          <t>351989</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>399400</t>
+          <t>398827</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13267,12 +13267,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>681382</t>
+          <t>683057</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>744636</t>
+          <t>745261</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13826,12 +13826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13861,12 +13861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13876,12 +13876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>480</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13989,12 +13989,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -14017,12 +14017,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>27735</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14032,12 +14032,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -14052,12 +14052,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>25297</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14067,12 +14067,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -14087,12 +14087,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27946</t>
+          <t>27769</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48883</t>
+          <t>48342</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14102,12 +14102,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -14130,12 +14130,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14145,12 +14145,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14165,12 +14165,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14180,12 +14180,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14200,12 +14200,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14215,12 +14215,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27483</t>
+          <t>26661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14371,12 +14371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14391,12 +14391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14406,12 +14406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14426,12 +14426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>35595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14441,12 +14441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -14469,12 +14469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14484,12 +14484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14504,12 +14504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16839</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30672</t>
+          <t>30966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14519,12 +14519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14539,12 +14539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33298</t>
+          <t>33317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54816</t>
+          <t>54440</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14554,12 +14554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,66%</t>
         </is>
       </c>
     </row>
@@ -14699,12 +14699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14734,12 +14734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14749,12 +14749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14769,12 +14769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13997</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -14812,12 +14812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14827,12 +14827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14847,12 +14847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14862,12 +14862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14882,12 +14882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28192</t>
+          <t>28336</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14897,12 +14897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -14925,12 +14925,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25585</t>
+          <t>26110</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14940,12 +14940,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14960,12 +14960,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24650</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14975,12 +14975,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14995,12 +14995,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>23919</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>43584</t>
+          <t>43860</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15010,12 +15010,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -15038,12 +15038,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56531</t>
+          <t>55455</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88855</t>
+          <t>88434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15053,12 +15053,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15073,12 +15073,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>67047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97582</t>
+          <t>97526</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15088,12 +15088,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15108,12 +15108,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133251</t>
+          <t>133077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178454</t>
+          <t>177994</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15123,12 +15123,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15547</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15201,12 +15201,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15221,12 +15221,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>21788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15236,12 +15236,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -15264,12 +15264,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15279,12 +15279,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15299,12 +15299,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>368</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15319,7 +15319,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -15377,12 +15377,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60073</t>
+          <t>61624</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>173368</t>
+          <t>158973</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15392,12 +15392,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15412,12 +15412,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59201</t>
+          <t>60693</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96246</t>
+          <t>98102</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15427,12 +15427,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15447,12 +15447,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>131922</t>
+          <t>132655</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>239026</t>
+          <t>247702</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15462,12 +15462,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -15490,12 +15490,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>203246</t>
+          <t>211065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281952</t>
+          <t>279856</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15505,12 +15505,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15525,12 +15525,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>297158</t>
+          <t>295683</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342798</t>
+          <t>343454</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15540,12 +15540,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>528271</t>
+          <t>522475</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>612419</t>
+          <t>611628</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15575,12 +15575,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,59%</t>
         </is>
       </c>
     </row>
@@ -15720,12 +15720,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15790,12 +15790,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15805,12 +15805,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -15838,7 +15838,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15903,12 +15903,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -15946,12 +15946,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16016,12 +16016,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16031,12 +16031,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -16059,12 +16059,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>16161</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16074,12 +16074,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16094,12 +16094,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16109,12 +16109,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>22982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16144,12 +16144,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -16398,12 +16398,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16413,12 +16413,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16433,12 +16433,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16448,12 +16448,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16468,12 +16468,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13417</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29429</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16483,12 +16483,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>119444</t>
+          <t>119612</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>133616</t>
+          <t>133938</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16526,12 +16526,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16546,12 +16546,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>146752</t>
+          <t>147737</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>164503</t>
+          <t>164845</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16561,12 +16561,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16581,12 +16581,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>273079</t>
+          <t>273017</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>295108</t>
+          <t>295926</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -16741,12 +16741,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16756,12 +16756,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16776,12 +16776,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16791,7 +16791,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -16811,12 +16811,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19992</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -16854,12 +16854,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16869,12 +16869,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16889,12 +16889,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23687</t>
+          <t>23791</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16924,12 +16924,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>35846</t>
+          <t>35115</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16939,12 +16939,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -16967,12 +16967,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>14256</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>30001</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17002,12 +17002,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>27079</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17017,12 +17017,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17037,12 +17037,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>29199</t>
+          <t>29142</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>51459</t>
+          <t>50930</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17052,12 +17052,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -17080,12 +17080,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>84079</t>
+          <t>82325</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>119095</t>
+          <t>118331</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17095,12 +17095,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17115,12 +17115,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>89898</t>
+          <t>88995</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>126105</t>
+          <t>125467</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17130,12 +17130,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17150,12 +17150,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>183371</t>
+          <t>183463</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>234829</t>
+          <t>236406</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17165,12 +17165,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -17193,12 +17193,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17208,12 +17208,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17228,12 +17228,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17243,12 +17243,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17263,12 +17263,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>33408</t>
+          <t>34617</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17278,12 +17278,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -17306,12 +17306,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>516</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17326,7 +17326,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17341,12 +17341,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17356,12 +17356,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17376,12 +17376,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17391,12 +17391,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -17419,12 +17419,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>77748</t>
+          <t>77792</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>180355</t>
+          <t>177596</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17454,12 +17454,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>82035</t>
+          <t>81235</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>120769</t>
+          <t>120137</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17469,12 +17469,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17489,12 +17489,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>169145</t>
+          <t>170729</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>284568</t>
+          <t>284220</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -17532,12 +17532,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>353199</t>
+          <t>344195</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>432726</t>
+          <t>431782</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17567,12 +17567,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>475308</t>
+          <t>474052</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>529194</t>
+          <t>528759</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17582,12 +17582,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17602,12 +17602,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>846646</t>
+          <t>843251</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>946512</t>
+          <t>945677</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17617,12 +17617,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
